--- a/samples/stock_count/재고실사_평택1창고.xlsx
+++ b/samples/stock_count/재고실사_평택1창고.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -57,7 +54,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -424,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -438,55 +435,81 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>창고</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>품번</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>품명</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>전산수량</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>실사수량</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>실사자</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>실사일</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>창고</t>
+          <t>평택1창고</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>품번</t>
+          <t>PK-3001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>품명</t>
+          <t>포장박스 대</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>단위</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>전산수량</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>실사수량</t>
-        </is>
+          <t>BOX</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>226</v>
+      </c>
+      <c r="F2" t="n">
+        <v>229</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>실사자</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>실사일</t>
-        </is>
+          <t>이영희</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>46291</v>
       </c>
     </row>
     <row r="3">
@@ -497,24 +520,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PK-3001</t>
+          <t>AS-5001</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>포장박스 대</t>
+          <t>모터 조립체</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>226</v>
+        <v>86</v>
       </c>
       <c r="F3" t="n">
-        <v>229</v>
+        <v>86</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -533,28 +556,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AS-5001</t>
+          <t>PK-3003</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>모터 조립체</t>
+          <t>스트레치 필름</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>ROLL</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>86</v>
-      </c>
-      <c r="F4" t="n">
-        <v>86</v>
+        <v>349</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>이영희</t>
+          <t>김철수</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
@@ -569,25 +589,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PK-3003</t>
+          <t>AS-5004</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>스트레치 필름</t>
+          <t>케이블 하네스</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ROLL</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>349</v>
+        <v>406</v>
+      </c>
+      <c r="F5" t="n">
+        <v>404</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>김철수</t>
+          <t>이영희</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
@@ -602,28 +625,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AS-5004</t>
+          <t>CH-6001</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>케이블 하네스</t>
+          <t>절삭유</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>406</v>
+        <v>170</v>
       </c>
       <c r="F6" t="n">
-        <v>404</v>
+        <v>170</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>이영희</t>
+          <t>김철수</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
@@ -638,12 +661,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CH-6001</t>
+          <t>RM-1002</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>절삭유</t>
+          <t>냉연강판 1.6T</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -652,14 +675,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>170</v>
-      </c>
-      <c r="F7" t="n">
-        <v>170</v>
+        <v>354</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>12개</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>김철수</t>
+          <t>이영희</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
@@ -674,30 +699,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RM-1002</t>
+          <t>CP-4001</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>냉연강판 1.6T</t>
+          <t>볼트 M8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>354</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>12개</t>
-        </is>
+        <v>474</v>
+      </c>
+      <c r="F8" t="n">
+        <v>474</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>이영희</t>
+          <t>김철수</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
@@ -712,12 +735,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CP-4001</t>
+          <t>CP-4004</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>볼트 M8</t>
+          <t>스프링 와셔 8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -726,10 +749,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>474</v>
+        <v>216</v>
       </c>
       <c r="F9" t="n">
-        <v>474</v>
+        <v>216</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -748,12 +771,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CP-4004</t>
+          <t>CP-4003</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>스프링 와셔 8</t>
+          <t>평와셔 8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -762,14 +785,14 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>216</v>
+        <v>424</v>
       </c>
       <c r="F10" t="n">
-        <v>216</v>
+        <v>424</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>김철수</t>
+          <t>이영희</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
@@ -784,24 +807,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CP-4003</t>
+          <t>PK-3002</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>평와셔 8</t>
+          <t>포장박스 소</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>424</v>
+        <v>-5</v>
       </c>
       <c r="F11" t="n">
-        <v>424</v>
+        <v>163</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -820,28 +843,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PK-3002</t>
+          <t>RM-2001</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>포장박스 소</t>
+          <t>알루미늄 봉 20Φ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>-5</v>
+        <v>416</v>
       </c>
       <c r="F12" t="n">
-        <v>163</v>
+        <v>416</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>이영희</t>
+          <t>김철수</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
@@ -856,28 +879,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RM-2001</t>
+          <t>AS-5002</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>알루미늄 봉 20Φ</t>
+          <t>센서 모듈</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>416</v>
+        <v>37</v>
       </c>
       <c r="F13" t="n">
-        <v>416</v>
+        <v>36</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>김철수</t>
+          <t>이영희</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
@@ -892,28 +915,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AS-5002</t>
+          <t>RM-1001</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>센서 모듈</t>
+          <t>냉연강판 1.2T</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>개</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>37</v>
+        <v>420</v>
       </c>
       <c r="F14" t="n">
-        <v>36</v>
+        <v>421</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>이영희</t>
+          <t>김철수</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
@@ -928,28 +951,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RM-1001</t>
+          <t>CP-4005</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>냉연강판 1.2T</t>
+          <t>리벳 4mm</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>420</v>
+        <v>64</v>
       </c>
       <c r="F15" t="n">
-        <v>421</v>
+        <v>64</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>김철수</t>
+          <t>이영희</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
@@ -964,67 +987,31 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CP-4005</t>
+          <t>RM-2002</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>리벳 4mm</t>
+          <t>알루미늄 봉 30Φ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>64</v>
+        <v>341</v>
       </c>
       <c r="F16" t="n">
-        <v>64</v>
+        <v>344</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>이영희</t>
+          <t>김철수</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>46291</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>평택1창고</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>RM-2002</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>알루미늄 봉 30Φ</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>341</v>
-      </c>
-      <c r="F17" t="n">
-        <v>344</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>김철수</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="n">
         <v>46291</v>
       </c>
     </row>
